--- a/Data/SK Material Expense.xlsx
+++ b/Data/SK Material Expense.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/SK Residence - Sundarapuram/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{2101CEFC-6734-441F-9C03-3A2887AAAB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5A42243-F66A-441E-A260-734F510D86AA}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{1FD95DAB-661B-4CC7-B0BF-1BFBE5BCE6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70A50B16-9403-42D4-9027-B725EE2EDA5E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Details" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Payment Details" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Material Details'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Material Details'!$A$1:$H$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Payment Details'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="80">
   <si>
     <t>DATE</t>
   </si>
@@ -295,6 +295,15 @@
   </si>
   <si>
     <t>Tiles bal</t>
+  </si>
+  <si>
+    <t>TILES PASTE</t>
+  </si>
+  <si>
+    <t>ICONIC TRADERS</t>
+  </si>
+  <si>
+    <t>paid 11500</t>
   </si>
 </sst>
 </file>
@@ -466,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -497,9 +506,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,8 +750,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C98D82A3-5B23-4660-9970-660A3AD2E7A3}" name="Table1" displayName="Table1" ref="A1:I66" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:I66" xr:uid="{C98D82A3-5B23-4660-9970-660A3AD2E7A3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C98D82A3-5B23-4660-9970-660A3AD2E7A3}" name="Table1" displayName="Table1" ref="A1:I71" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:I71" xr:uid="{C98D82A3-5B23-4660-9970-660A3AD2E7A3}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{29839E6D-9721-413F-B2A1-257A999278CF}" name="DATE" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{4F093DBA-8C7A-4DCC-81B9-13C725A36358}" name="CATEGORY" dataDxfId="7"/>
@@ -1025,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="25.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
@@ -2804,6 +2811,134 @@
         <v>4150</v>
       </c>
       <c r="I66" s="18"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="17">
+        <v>46154</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18">
+        <f>IFERROR(VLOOKUP(B67,'Reference Table'!$A$2:$C$20,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="19"/>
+      <c r="H67" s="20">
+        <v>4550</v>
+      </c>
+      <c r="I67" s="18"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="17">
+        <v>45789</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18">
+        <f>IFERROR(VLOOKUP(B68,'Reference Table'!$A$2:$C$20,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="19"/>
+      <c r="H68" s="20">
+        <v>2845</v>
+      </c>
+      <c r="I68" s="18"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="17">
+        <v>46165</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E69" s="18">
+        <v>50</v>
+      </c>
+      <c r="F69" s="18" t="str">
+        <f>IFERROR(VLOOKUP(B69,'Reference Table'!$A$2:$C$20,2,FALSE),"")</f>
+        <v>BAGS</v>
+      </c>
+      <c r="G69" s="19">
+        <v>295</v>
+      </c>
+      <c r="H69" s="20">
+        <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
+        <v>14750</v>
+      </c>
+      <c r="I69" s="18"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="17">
+        <v>46177</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="18">
+        <v>20</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="19">
+        <v>580</v>
+      </c>
+      <c r="H70" s="20">
+        <f>Table1[[#This Row],[RATE]]*Table1[[#This Row],[QTY]]</f>
+        <v>11600</v>
+      </c>
+      <c r="I70" s="18"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="17">
+        <v>46179</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E71" s="18">
+        <v>20</v>
+      </c>
+      <c r="F71" s="18" t="str">
+        <f>IFERROR(VLOOKUP(B71,'Reference Table'!$A$2:$C$20,2,FALSE),"")</f>
+        <v>BAGS</v>
+      </c>
+      <c r="G71" s="19">
+        <v>295</v>
+      </c>
+      <c r="H71" s="20">
+        <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
+        <v>5900</v>
+      </c>
+      <c r="I71" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2827,7 +2962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7945D8E7-2C2E-4C89-B38E-C74186D29A9E}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -2970,14 +3105,25 @@
       <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="6" t="s">
         <v>73</v>
       </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2986,7 +3132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC52B97-F8EC-489B-AAAD-008E3D44EA2D}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -3010,18 +3156,18 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="str" cm="1">
-        <f t="array" ref="A2:A17">_xlfn.UNIQUE('Material Details'!B2:B1010)</f>
+        <f t="array" ref="A2:A18">_xlfn.UNIQUE('Material Details'!B2:B1009)</f>
         <v>M-SAND</v>
       </c>
       <c r="B2" s="6">
-        <f>SUMIF('Material Details'!B2:B1010,A2,'Material Details'!E2:E1010)</f>
+        <f>SUMIF('Material Details'!B2:B1009,A2,'Material Details'!E2:E1009)</f>
         <v>38</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="7">
-        <f>SUMIF('Material Details'!B2:B1010,A2,'Material Details'!H2:H1010)</f>
+        <f>SUMIF('Material Details'!B2:B1009,A2,'Material Details'!H2:H1009)</f>
         <v>194750</v>
       </c>
     </row>
@@ -3030,14 +3176,14 @@
         <v>40 MM METAL</v>
       </c>
       <c r="B3" s="6">
-        <f>SUMIF('Material Details'!B3:B1011,A3,'Material Details'!E3:E1011)</f>
+        <f>SUMIF('Material Details'!B3:B1010,A3,'Material Details'!E3:E1010)</f>
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="7">
-        <f>SUMIF('Material Details'!B3:B1011,A3,'Material Details'!H3:H1011)</f>
+        <f>SUMIF('Material Details'!B3:B1010,A3,'Material Details'!H3:H1010)</f>
         <v>17800</v>
       </c>
     </row>
@@ -3046,14 +3192,14 @@
         <v>STEEL</v>
       </c>
       <c r="B4" s="6">
-        <f>SUMIF('Material Details'!B4:B1012,A4,'Material Details'!E4:E1012)</f>
+        <f>SUMIF('Material Details'!B4:B1011,A4,'Material Details'!E4:E1011)</f>
         <v>7075</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="7">
-        <f>SUMIF('Material Details'!B4:B1012,A4,'Material Details'!H4:H1012)</f>
+        <f>SUMIF('Material Details'!B4:B1011,A4,'Material Details'!H4:H1011)</f>
         <v>565821.31999999995</v>
       </c>
     </row>
@@ -3062,15 +3208,15 @@
         <v>CEMENT</v>
       </c>
       <c r="B5" s="6">
-        <f>SUMIF('Material Details'!B5:B1013,A5,'Material Details'!E5:E1013)</f>
-        <v>1015</v>
+        <f>SUMIF('Material Details'!B5:B1012,A5,'Material Details'!E5:E1012)</f>
+        <v>1085</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="7">
-        <f>SUMIF('Material Details'!B5:B1013,A5,'Material Details'!H5:H1013)</f>
-        <v>294025</v>
+        <f>SUMIF('Material Details'!B5:B1012,A5,'Material Details'!H5:H1012)</f>
+        <v>314675</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -3078,14 +3224,14 @@
         <v>20 MM JALLY</v>
       </c>
       <c r="B6" s="6">
-        <f>SUMIF('Material Details'!B6:B1014,A6,'Material Details'!E6:E1014)</f>
+        <f>SUMIF('Material Details'!B6:B1013,A6,'Material Details'!E6:E1013)</f>
         <v>24</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="7">
-        <f>SUMIF('Material Details'!B6:B1014,A6,'Material Details'!H6:H1014)</f>
+        <f>SUMIF('Material Details'!B6:B1013,A6,'Material Details'!H6:H1013)</f>
         <v>108000</v>
       </c>
     </row>
@@ -3094,14 +3240,14 @@
         <v>BRICK</v>
       </c>
       <c r="B7" s="6">
-        <f>SUMIF('Material Details'!B7:B1015,A7,'Material Details'!E7:E1015)</f>
+        <f>SUMIF('Material Details'!B7:B1014,A7,'Material Details'!E7:E1014)</f>
         <v>33600</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="7">
-        <f>SUMIF('Material Details'!B7:B1015,A7,'Material Details'!H7:H1015)</f>
+        <f>SUMIF('Material Details'!B7:B1014,A7,'Material Details'!H7:H1014)</f>
         <v>388800</v>
       </c>
     </row>
@@ -3110,14 +3256,14 @@
         <v>P-SAND</v>
       </c>
       <c r="B8" s="6">
-        <f>SUMIF('Material Details'!B9:B1016,A8,'Material Details'!E9:E1016)</f>
+        <f>SUMIF('Material Details'!B9:B1015,A8,'Material Details'!E9:E1015)</f>
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="7">
-        <f>SUMIF('Material Details'!B8:B1016,A8,'Material Details'!H8:H1016)</f>
+        <f>SUMIF('Material Details'!B8:B1015,A8,'Material Details'!H8:H1015)</f>
         <v>69000</v>
       </c>
     </row>
@@ -3126,14 +3272,14 @@
         <v>GRAVEL</v>
       </c>
       <c r="B9" s="6">
-        <f>SUMIF('Material Details'!B10:B1017,A9,'Material Details'!E10:E1017)</f>
+        <f>SUMIF('Material Details'!B10:B1016,A9,'Material Details'!E10:E1016)</f>
         <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="7">
-        <f>SUMIF('Material Details'!B9:B1017,A9,'Material Details'!H9:H1017)</f>
+        <f>SUMIF('Material Details'!B9:B1016,A9,'Material Details'!H9:H1016)</f>
         <v>54000</v>
       </c>
     </row>
@@ -3142,14 +3288,14 @@
         <v>ELECTRICAL</v>
       </c>
       <c r="B10" s="6">
-        <f>SUMIF('Material Details'!B11:B1018,A10,'Material Details'!E11:E1018)</f>
+        <f>SUMIF('Material Details'!B11:B1017,A10,'Material Details'!E11:E1017)</f>
         <v>0</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="7">
-        <f>SUMIF('Material Details'!B10:B1018,A10,'Material Details'!H10:H1018)</f>
+        <f>SUMIF('Material Details'!B10:B1017,A10,'Material Details'!H10:H1017)</f>
         <v>40271</v>
       </c>
     </row>
@@ -3158,14 +3304,14 @@
         <v>OTHERS</v>
       </c>
       <c r="B11" s="6">
-        <f>SUMIF('Material Details'!B12:B1019,A11,'Material Details'!E12:E1019)</f>
+        <f>SUMIF('Material Details'!B12:B1018,A11,'Material Details'!E12:E1018)</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="7">
-        <f>SUMIF('Material Details'!B11:B1019,A11,'Material Details'!H11:H1019)</f>
+        <f>SUMIF('Material Details'!B11:B1018,A11,'Material Details'!H11:H1018)</f>
         <v>1310</v>
       </c>
     </row>
@@ -3174,50 +3320,88 @@
         <v>BABY CHIPS</v>
       </c>
       <c r="B12" s="6">
-        <f>SUMIF('Material Details'!B13:B1020,A12,'Material Details'!E13:E1020)</f>
+        <f>SUMIF('Material Details'!B13:B1019,A12,'Material Details'!E13:E1019)</f>
         <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="7">
-        <f>SUMIF('Material Details'!B12:B1020,A12,'Material Details'!H12:H1020)</f>
+        <f>SUMIF('Material Details'!B12:B1019,A12,'Material Details'!H12:H1019)</f>
         <v>9500</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="str">
+      <c r="A13" s="6" t="str">
         <v>BRICK-FLYASH</v>
       </c>
       <c r="B13" s="6">
-        <f>SUMIF('Material Details'!B14:B1021,A13,'Material Details'!E14:E1021)</f>
+        <f>SUMIF('Material Details'!B14:B1020,A13,'Material Details'!E14:E1020)</f>
         <v>3000</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="7">
-        <f>SUMIF('Material Details'!B13:B1021,A13,'Material Details'!H13:H1021)</f>
+        <f>SUMIF('Material Details'!B13:B1020,A13,'Material Details'!H13:H1020)</f>
         <v>24900.000000000004</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="str">
+      <c r="A14" s="6" t="str">
         <v>PAINTING</v>
       </c>
+      <c r="B14" s="6">
+        <f>SUMIF('Material Details'!B15:B1021,A14,'Material Details'!E15:E1021)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="7">
+        <f>SUMIF('Material Details'!B14:B1021,A14,'Material Details'!H14:H1021)</f>
+        <v>13230</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="str">
+      <c r="A15" s="6" t="str">
         <v>PLUMBING</v>
       </c>
+      <c r="B15" s="6">
+        <f>SUMIF('Material Details'!B16:B1022,A15,'Material Details'!E16:E1022)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="7">
+        <f>SUMIF('Material Details'!B15:B1022,A15,'Material Details'!H15:H1022)</f>
+        <v>55983</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="str">
+      <c r="A16" s="6" t="str">
         <v>TILES</v>
       </c>
+      <c r="B16" s="6">
+        <f>SUMIF('Material Details'!B17:B1023,A16,'Material Details'!E17:E1023)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="7">
+        <f>SUMIF('Material Details'!B16:B1023,A16,'Material Details'!H16:H1023)</f>
+        <v>230845</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="A17" t="str">
+        <v>TILES PASTE</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>0</v>
       </c>
     </row>
@@ -3228,7 +3412,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96697B0-05D6-4BCA-A61B-0D246D1FF2DE}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
@@ -3253,20 +3437,20 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="str" cm="1">
-        <f t="array" ref="A2:A11">_xlfn.UNIQUE('Material Details'!D2:D1010)</f>
+        <f t="array" ref="A2:A12">_xlfn.UNIQUE('Material Details'!D2:D1009)</f>
         <v>RSK</v>
       </c>
       <c r="B2" s="7">
-        <f>SUMIF('Material Details'!D2:D1010,A2,'Material Details'!H2:H1010)</f>
+        <f>SUMIF('Material Details'!D2:D1009,A2,'Material Details'!H2:H1009)</f>
         <v>453050</v>
       </c>
       <c r="C2" s="7">
         <f>SUMIF('Payment Details'!B2:B992,'Vendor Balance Sheet'!A2,'Payment Details'!C2:C992)</f>
-        <v>400000</v>
+        <v>450000</v>
       </c>
       <c r="D2" s="7">
         <f>B2-C2</f>
-        <v>53050</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -3274,7 +3458,7 @@
         <v>AK STEELS</v>
       </c>
       <c r="B3" s="7">
-        <f>SUMIF('Material Details'!D2:D1010,A3,'Material Details'!H2:H1010)</f>
+        <f>SUMIF('Material Details'!D2:D1009,A3,'Material Details'!H2:H1009)</f>
         <v>565821.31999999995</v>
       </c>
       <c r="C3" s="7">
@@ -3291,16 +3475,16 @@
         <v>PALANI MURUGAN</v>
       </c>
       <c r="B4" s="7">
-        <f>SUMIF('Material Details'!D3:D1011,A4,'Material Details'!H3:H1011)</f>
+        <f>SUMIF('Material Details'!D3:D1010,A4,'Material Details'!H3:H1010)</f>
         <v>224025</v>
       </c>
       <c r="C4" s="7">
         <f>SUMIF('Payment Details'!B2:B992,'Vendor Balance Sheet'!A4,'Payment Details'!C2:C992)</f>
-        <v>221350</v>
+        <v>224025</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>2675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -3308,7 +3492,7 @@
         <v>VEL BRICK</v>
       </c>
       <c r="B5" s="7">
-        <f>SUMIF('Material Details'!D4:D1012,A5,'Material Details'!H4:H1012)</f>
+        <f>SUMIF('Material Details'!D4:D1011,A5,'Material Details'!H4:H1011)</f>
         <v>388800</v>
       </c>
       <c r="C5" s="7">
@@ -3325,16 +3509,16 @@
         <v>RAMDEV ELECTRICALS</v>
       </c>
       <c r="B6" s="7">
-        <f>SUMIF('Material Details'!D5:D1013,A6,'Material Details'!H5:H1013)</f>
-        <v>105244</v>
+        <f>SUMIF('Material Details'!D5:D1012,A6,'Material Details'!H5:H1012)</f>
+        <v>109794</v>
       </c>
       <c r="C6" s="7">
         <f>SUMIF('Payment Details'!B3:B994,'Vendor Balance Sheet'!A6,'Payment Details'!C3:C994)</f>
-        <v>73550</v>
+        <v>103550</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>31694</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -3342,7 +3526,7 @@
         <v>NV ASSOCIATES</v>
       </c>
       <c r="B7" s="7">
-        <f>SUMIF('Material Details'!D6:D1014,A7,'Material Details'!H6:H1014)</f>
+        <f>SUMIF('Material Details'!D6:D1013,A7,'Material Details'!H6:H1013)</f>
         <v>41250</v>
       </c>
       <c r="C7" s="7">
@@ -3359,16 +3543,16 @@
         <v>CHAKRA TRADERS</v>
       </c>
       <c r="B8" s="7">
-        <f>SUMIF('Material Details'!D7:D1015,A8,'Material Details'!H7:H1015)</f>
-        <v>28750</v>
+        <f>SUMIF('Material Details'!D7:D1014,A8,'Material Details'!H7:H1014)</f>
+        <v>49400</v>
       </c>
       <c r="C8" s="7">
         <f>SUMIF('Payment Details'!B5:B996,'Vendor Balance Sheet'!A8,'Payment Details'!C5:C996)</f>
-        <v>13500</v>
+        <v>43500</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" ref="D8:D10" si="1">B8-C8</f>
-        <v>15250</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
@@ -3390,7 +3574,7 @@
         <v>AMARUN FLYASH</v>
       </c>
       <c r="B10" s="7">
-        <f>SUMIF('Material Details'!D9:D1017,A10,'Material Details'!H9:H1017)</f>
+        <f>SUMIF('Material Details'!D9:D1016,A10,'Material Details'!H9:H1016)</f>
         <v>24900.000000000004</v>
       </c>
       <c r="C10" s="7">
@@ -3403,19 +3587,36 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="str">
+      <c r="A11" s="6" t="str">
         <v>LAKSHMI CERAMICS</v>
       </c>
       <c r="B11" s="7">
-        <f>SUMIF('Material Details'!D10:D1018,A11,'Material Details'!H10:H1018)</f>
-        <v>228000</v>
+        <f>SUMIF('Material Details'!D10:D1017,A11,'Material Details'!H10:H1017)</f>
+        <v>230845</v>
       </c>
       <c r="C11" s="7">
         <f>SUMIF('Payment Details'!B8:B999,'Vendor Balance Sheet'!A11,'Payment Details'!C8:C999)</f>
-        <v>228000</v>
+        <v>230845</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" ref="D11" si="2">B11-C11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="str">
+        <v>ICONIC TRADERS</v>
+      </c>
+      <c r="B12" s="7">
+        <f>SUMIF('Material Details'!D11:D1018,A12,'Material Details'!H11:H1018)</f>
+        <v>11600</v>
+      </c>
+      <c r="C12" s="7">
+        <f>SUMIF('Payment Details'!B9:B1000,'Vendor Balance Sheet'!A12,'Payment Details'!C9:C1000)</f>
+        <v>11600</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" ref="D12" si="3">B12-C12</f>
         <v>0</v>
       </c>
     </row>
@@ -3426,7 +3627,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B843CC5F-739E-45E9-AC65-8442CF552E38}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="3"/>
@@ -4219,7 +4420,7 @@
       <c r="A40" s="5">
         <v>46151</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C40" s="7">
@@ -4231,7 +4432,7 @@
       <c r="E40" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4239,7 +4440,7 @@
       <c r="A41" s="5">
         <v>46151</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C41" s="7">
@@ -4251,7 +4452,7 @@
       <c r="E41" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4259,7 +4460,7 @@
       <c r="A42" s="5">
         <v>46151</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C42" s="7">
@@ -4271,8 +4472,125 @@
       <c r="E42" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="7" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="5">
+        <v>46154</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2845</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="7">
+        <v>2675</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="5">
+        <v>46179</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="7">
+        <v>11600</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="4">
+        <v>30000</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
